--- a/Config/Datas/cult_ancient_seat.xlsx
+++ b/Config/Datas/cult_ancient_seat.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cult_ancient_seat" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cult_seat_tech_node" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cult_seat_tech_node_level" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cult_ancient_seat" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cult_seat_tech_node" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cult_seat_tech_node_level" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,11 @@
           <t>default_unlocked</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unlock_conds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,6 +506,11 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),CommonCheckCond</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,6 +553,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -585,6 +600,10 @@
           <t>默认点亮</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -616,6 +635,7 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -646,6 +666,11 @@
       </c>
       <c r="H7" t="b">
         <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10,1,0,0,0,, </t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -876,7 +901,6 @@
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1027,7 +1051,6 @@
       <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>80</v>
       </c>
